--- a/tests/gii.xlsx
+++ b/tests/gii.xlsx
@@ -38,7 +38,7 @@
     <t>寄售出库（随货同行）单</t>
   </si>
   <si>
-    <t>器械</t>
+    <t>salemode</t>
   </si>
   <si>
     <t>发货日期：</t>
